--- a/agentic-qe-mvp/demo-artifacts/flow-2-incremental-CYC-2/08-report/CYC-2-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-incremental-CYC-2/08-report/CYC-2-cycle-report.xlsx
@@ -172,7 +172,7 @@
     <t>sri465inno/uc-agentic-quality-engineering@demo/commission-engine-v2 (6ccd807)</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/commission-engine-v2 (6ccd807) at 2026-09-28T21:39:41.708Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/commission-engine-v2 (6ccd807) at 2026-09-28T21:43:27.440Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -1080,7 +1080,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-09-28T21:39:43.429Z</t>
+    <t>2026-09-28T21:43:29.081Z</t>
   </si>
   <si>
     <t>14 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -1092,7 +1092,7 @@
     <t>Sam Lee</t>
   </si>
   <si>
-    <t>2026-09-28T21:39:43.437Z</t>
+    <t>2026-09-28T21:43:29.089Z</t>
   </si>
   <si>
     <t>4 requirements, 5 test cases, 4 scripts merged: BL-1 v1 -&gt; v2</t>
@@ -3667,7 +3667,7 @@
         <v>268</v>
       </c>
       <c r="E2" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -3685,7 +3685,7 @@
         <v>268</v>
       </c>
       <c r="E3" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -3703,7 +3703,7 @@
         <v>268</v>
       </c>
       <c r="E4" s="2">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -3793,7 +3793,7 @@
         <v>268</v>
       </c>
       <c r="E9" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -3811,7 +3811,7 @@
         <v>268</v>
       </c>
       <c r="E10" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -3829,7 +3829,7 @@
         <v>268</v>
       </c>
       <c r="E11" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -3847,7 +3847,7 @@
         <v>268</v>
       </c>
       <c r="E12" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -3903,7 +3903,7 @@
         <v>268</v>
       </c>
       <c r="E15" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F15" s="2"/>
     </row>
@@ -3957,7 +3957,7 @@
         <v>268</v>
       </c>
       <c r="E18" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -3975,7 +3975,7 @@
         <v>268</v>
       </c>
       <c r="E19" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F19" s="2"/>
     </row>

--- a/agentic-qe-mvp/demo-artifacts/flow-2-incremental-CYC-2/08-report/CYC-2-cycle-report.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-2-incremental-CYC-2/08-report/CYC-2-cycle-report.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="416">
   <si>
     <t>Metric</t>
   </si>
@@ -172,7 +172,7 @@
     <t>sri465inno/uc-agentic-quality-engineering@demo/commission-engine-v2 (6ccd807)</t>
   </si>
   <si>
-    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/commission-engine-v2 (6ccd807) at 2026-09-28T21:43:27.440Z</t>
+    <t>Pulled live from GitHub: git clone of sri465inno/uc-agentic-quality-engineering@demo/commission-engine-v2 (6ccd807) at 2026-09-29T17:20:30.020Z</t>
   </si>
   <si>
     <t>ID</t>
@@ -1080,7 +1080,7 @@
     <t>Priya Shah</t>
   </si>
   <si>
-    <t>2026-09-28T21:43:29.081Z</t>
+    <t>2026-09-29T17:20:31.626Z</t>
   </si>
   <si>
     <t>14 requirements approved; 0 excluded; 0 conflict(s) resolved</t>
@@ -1092,7 +1092,7 @@
     <t>Sam Lee</t>
   </si>
   <si>
-    <t>2026-09-28T21:43:29.089Z</t>
+    <t>2026-09-29T17:20:31.635Z</t>
   </si>
   <si>
     <t>4 requirements, 5 test cases, 4 scripts merged: BL-1 v1 -&gt; v2</t>
@@ -1182,6 +1182,21 @@
     <t>input-normalisation.md</t>
   </si>
   <si>
+    <t>input-review</t>
+  </si>
+  <si>
+    <t>Input review before the human gate</t>
+  </si>
+  <si>
+    <t>What the review agent checks in the project inputs and how it words its suggestions for the reviewer.</t>
+  </si>
+  <si>
+    <t>review-agent</t>
+  </si>
+  <si>
+    <t>input-review.md</t>
+  </si>
+  <si>
     <t>test-case-authoring</t>
   </si>
   <si>
@@ -1197,6 +1212,21 @@
     <t>test-case-authoring.md</t>
   </si>
   <si>
+    <t>testing-regression</t>
+  </si>
+  <si>
+    <t>Regression pack</t>
+  </si>
+  <si>
+    <t>Steers the design and execution agents to keep and re-run the full pack so nothing that worked before breaks.</t>
+  </si>
+  <si>
+    <t>testcases, scripts, execution</t>
+  </si>
+  <si>
+    <t>testing-regression.md</t>
+  </si>
+  <si>
     <t>traceability-handover</t>
   </si>
   <si>
@@ -1239,6 +1269,9 @@
     <t>statements: delivered; gaps: delivered; conflicts: delivered</t>
   </si>
   <si>
+    <t>suggestions: delivered</t>
+  </si>
+  <si>
     <t>Delta classification</t>
   </si>
   <si>
@@ -1263,22 +1296,25 @@
     <t>Test case agent</t>
   </si>
   <si>
-    <t>incremental-merge, test-case-authoring, traceability-handover</t>
-  </si>
-  <si>
-    <t>functional: delivered; nonFunctional: delivered</t>
+    <t>incremental-merge, test-case-authoring, testing-regression, traceability-handover</t>
+  </si>
+  <si>
+    <t>functional: delivered; nonFunctional: delivered; regressionPack: delivered</t>
   </si>
   <si>
     <t>Automation script agent</t>
   </si>
   <si>
-    <t>automation-script-conventions, incremental-merge, traceability-handover</t>
+    <t>automation-script-conventions, incremental-merge, testing-regression, traceability-handover</t>
   </si>
   <si>
     <t>specs: delivered</t>
   </si>
   <si>
     <t>Execution agent (Playwright, real run)</t>
+  </si>
+  <si>
+    <t>testing-regression, traceability-handover</t>
   </si>
   <si>
     <t>results: delivered</t>
@@ -1896,7 +1932,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -2042,6 +2078,40 @@
         <v>373</v>
       </c>
     </row>
+    <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2050,7 +2120,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -2062,172 +2132,186 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>118</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>383</v>
-      </c>
+        <v>392</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>118</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>118</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>118</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>381</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>118</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>118</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>369</v>
+        <v>405</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>118</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>118</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>118</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>403</v>
+        <v>412</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -3667,7 +3751,7 @@
         <v>268</v>
       </c>
       <c r="E2" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F2" s="2"/>
     </row>
@@ -3685,7 +3769,7 @@
         <v>268</v>
       </c>
       <c r="E3" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -3703,7 +3787,7 @@
         <v>268</v>
       </c>
       <c r="E4" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -3721,7 +3805,7 @@
         <v>268</v>
       </c>
       <c r="E5" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" s="2"/>
     </row>
@@ -3793,7 +3877,7 @@
         <v>268</v>
       </c>
       <c r="E9" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F9" s="2"/>
     </row>
@@ -3811,7 +3895,7 @@
         <v>268</v>
       </c>
       <c r="E10" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10" s="2"/>
     </row>
@@ -3829,7 +3913,7 @@
         <v>268</v>
       </c>
       <c r="E11" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" s="2"/>
     </row>
@@ -3847,7 +3931,7 @@
         <v>268</v>
       </c>
       <c r="E12" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F12" s="2"/>
     </row>
@@ -3865,7 +3949,7 @@
         <v>268</v>
       </c>
       <c r="E13" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F13" s="2"/>
     </row>
@@ -3903,7 +3987,7 @@
         <v>268</v>
       </c>
       <c r="E15" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F15" s="2"/>
     </row>
@@ -3957,7 +4041,7 @@
         <v>268</v>
       </c>
       <c r="E18" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F18" s="2"/>
     </row>
@@ -3975,7 +4059,7 @@
         <v>268</v>
       </c>
       <c r="E19" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F19" s="2"/>
     </row>
